--- a/tests/fixtures/06_merged_cells/06_merged_cells_pattern-from-claude.xlsx
+++ b/tests/fixtures/06_merged_cells/06_merged_cells_pattern-from-claude.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
